--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0646EA7-75DD-47B2-9997-FCF1A6955770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E3EF13-93DC-4571-8BAC-B62B1B2D5F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
